--- a/salidas/empresas/NOV.xlsx
+++ b/salidas/empresas/NOV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.26826095581055</v>
+        <v>26.26827049255371</v>
       </c>
       <c r="C2" t="n">
         <v>34.29666519165039</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>21.02291107177734</v>
+        <v>21.02289962768555</v>
       </c>
       <c r="C3" t="n">
         <v>27.44815063476562</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>22.14173316955566</v>
+        <v>22.14172554016113</v>
       </c>
       <c r="C4" t="n">
         <v>28.90892791748047</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.81651496887207</v>
+        <v>23.81652450561523</v>
       </c>
       <c r="C5" t="n">
         <v>31.0955810546875</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.81164169311523</v>
+        <v>22.81164360046387</v>
       </c>
       <c r="C6" t="n">
         <v>29.78358840942383</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.86547470092773</v>
+        <v>21.86548042297363</v>
       </c>
       <c r="C7" t="n">
         <v>28.54824256896973</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>23.15005874633789</v>
+        <v>23.15005493164062</v>
       </c>
       <c r="C8" t="n">
         <v>30.22542762756348</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>22.54920387268066</v>
+        <v>22.54920768737793</v>
       </c>
       <c r="C9" t="n">
         <v>29.44093894958496</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.21830940246582</v>
+        <v>20.21831321716309</v>
       </c>
       <c r="C10" t="n">
         <v>26.39765548706055</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.85715293884277</v>
+        <v>20.85714530944824</v>
       </c>
       <c r="C11" t="n">
         <v>27.23174095153809</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>21.12649345397949</v>
+        <v>21.12649917602539</v>
       </c>
       <c r="C13" t="n">
         <v>27.58340835571289</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>20.94003105163574</v>
+        <v>20.94002532958984</v>
       </c>
       <c r="C14" t="n">
         <v>27.33994674682617</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>24.04787826538086</v>
+        <v>24.04788398742676</v>
       </c>
       <c r="C15" t="n">
         <v>31.39765548706055</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>26.86220550537109</v>
+        <v>26.8621997833252</v>
       </c>
       <c r="C16" t="n">
         <v>35.07213592529297</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>29.3001537322998</v>
+        <v>29.30014419555664</v>
       </c>
       <c r="C17" t="n">
         <v>38.25518417358398</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>32.61519241333008</v>
+        <v>32.61518096923828</v>
       </c>
       <c r="C18" t="n">
         <v>42.58340835571289</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>35.99585723876953</v>
+        <v>35.995849609375</v>
       </c>
       <c r="C19" t="n">
         <v>46.99729537963867</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>44.20059585571289</v>
+        <v>44.20056915283203</v>
       </c>
       <c r="C21" t="n">
         <v>57.70964813232422</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>49.89831924438477</v>
+        <v>49.8983039855957</v>
       </c>
       <c r="C22" t="n">
         <v>65.14878082275391</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>50.58203125</v>
+        <v>50.58203506469727</v>
       </c>
       <c r="C23" t="n">
         <v>66.04148101806641</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>47.06670761108398</v>
+        <v>47.06669998168945</v>
       </c>
       <c r="C24" t="n">
         <v>61.45175933837891</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>50.73397827148438</v>
+        <v>50.73396301269531</v>
       </c>
       <c r="C25" t="n">
         <v>66.23985290527344</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>43.02651214599609</v>
+        <v>43.02650451660156</v>
       </c>
       <c r="C27" t="n">
         <v>56.17673492431641</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>40.31921005249023</v>
+        <v>40.31922149658203</v>
       </c>
       <c r="C28" t="n">
         <v>52.64202117919922</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>47.2739143371582</v>
+        <v>47.27390289306641</v>
       </c>
       <c r="C29" t="n">
         <v>61.72227096557617</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>57.54362869262695</v>
+        <v>57.54360580444336</v>
       </c>
       <c r="C30" t="n">
         <v>75.13074493408203</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>61.27305221557617</v>
+        <v>61.27305603027344</v>
       </c>
       <c r="C31" t="n">
         <v>80</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>54.30453872680664</v>
+        <v>54.30455780029297</v>
       </c>
       <c r="C32" t="n">
         <v>70.90171051025391</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>50.92042922973633</v>
+        <v>50.92044448852539</v>
       </c>
       <c r="C33" t="n">
         <v>66.48331451416016</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>34.69055557250977</v>
+        <v>34.69054412841797</v>
       </c>
       <c r="C34" t="n">
         <v>45.29305648803711</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.64305114746094</v>
+        <v>20.64305686950684</v>
       </c>
       <c r="C35" t="n">
         <v>26.95220947265625</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>19.53803825378418</v>
+        <v>19.53803443908691</v>
       </c>
       <c r="C36" t="n">
         <v>25.50946807861328</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.87909698486328</v>
+        <v>16.87909507751465</v>
       </c>
       <c r="C37" t="n">
         <v>22.03787231445312</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>18.2603645324707</v>
+        <v>18.26036262512207</v>
       </c>
       <c r="C38" t="n">
         <v>23.8412971496582</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>18.46064949035645</v>
+        <v>18.46064376831055</v>
       </c>
       <c r="C39" t="n">
         <v>24.1027946472168</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.82810401916504</v>
+        <v>19.82810592651367</v>
       </c>
       <c r="C40" t="n">
         <v>25.88818740844727</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.91239929199219</v>
+        <v>20.91240119934082</v>
       </c>
       <c r="C41" t="n">
         <v>27.30387687683105</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>26.67229652404785</v>
+        <v>26.67228507995605</v>
       </c>
       <c r="C42" t="n">
         <v>34.82416534423828</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>22.55611038208008</v>
+        <v>22.55610656738281</v>
       </c>
       <c r="C43" t="n">
         <v>29.44995498657227</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>24.82138824462891</v>
+        <v>24.82139015197754</v>
       </c>
       <c r="C44" t="n">
         <v>32.40757369995117</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>25.10454750061035</v>
+        <v>25.10455894470215</v>
       </c>
       <c r="C45" t="n">
         <v>32.77727890014648</v>
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>28.3090934753418</v>
+        <v>28.30908012390137</v>
       </c>
       <c r="C47" t="n">
         <v>36.96122741699219</v>
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>31.24377632141113</v>
+        <v>31.2437801361084</v>
       </c>
       <c r="C49" t="n">
         <v>39.75653839111328</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.98322868347168</v>
+        <v>28.98322105407715</v>
       </c>
       <c r="C50" t="n">
         <v>36.88007354736328</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>28.82281303405762</v>
+        <v>28.82280158996582</v>
       </c>
       <c r="C52" t="n">
         <v>36.59152221679688</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>31.27324867248535</v>
+        <v>31.27325439453125</v>
       </c>
       <c r="C53" t="n">
         <v>39.70243453979492</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>27.0826530456543</v>
+        <v>27.08266067504883</v>
       </c>
       <c r="C54" t="n">
         <v>34.38232421875</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>23.55521011352539</v>
+        <v>23.55521583557129</v>
       </c>
       <c r="C55" t="n">
         <v>29.81965637207031</v>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>26.8032283782959</v>
+        <v>26.80322265625</v>
       </c>
       <c r="C57" t="n">
         <v>33.93146896362305</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>31.75555229187012</v>
+        <v>31.75553703308105</v>
       </c>
       <c r="C58" t="n">
         <v>40.09918975830078</v>
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>43.76652145385742</v>
+        <v>43.76651382446289</v>
       </c>
       <c r="C60" t="n">
         <v>55.26600646972656</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>48.10882568359375</v>
+        <v>48.10882949829102</v>
       </c>
       <c r="C61" t="n">
         <v>60.64021682739258</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>52.86606597900391</v>
+        <v>52.86606216430664</v>
       </c>
       <c r="C62" t="n">
         <v>66.63661193847656</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>56.92222213745117</v>
+        <v>56.92222595214844</v>
       </c>
       <c r="C63" t="n">
         <v>71.74932098388672</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>56.78586196899414</v>
+        <v>56.78586959838867</v>
       </c>
       <c r="C64" t="n">
         <v>71.47881317138672</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>54.93766021728516</v>
+        <v>54.93765640258789</v>
       </c>
       <c r="C65" t="n">
         <v>69.15238952636719</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>51.99341201782227</v>
+        <v>51.99342346191406</v>
       </c>
       <c r="C66" t="n">
         <v>65.44635009765625</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>56.11318969726562</v>
+        <v>56.11320114135742</v>
       </c>
       <c r="C67" t="n">
         <v>70.52299499511719</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>57.80642318725586</v>
+        <v>57.80642700195312</v>
       </c>
       <c r="C68" t="n">
         <v>72.65103912353516</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>47.43901062011719</v>
+        <v>47.43900680541992</v>
       </c>
       <c r="C69" t="n">
         <v>59.62128067016602</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>36.81232070922852</v>
+        <v>36.81230545043945</v>
       </c>
       <c r="C70" t="n">
         <v>46.18575286865234</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>51.26556015014648</v>
+        <v>51.26557159423828</v>
       </c>
       <c r="C71" t="n">
         <v>64.31920623779297</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>51.62306594848633</v>
+        <v>51.62305068969727</v>
       </c>
       <c r="C72" t="n">
         <v>64.65283966064453</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>48.95190811157227</v>
+        <v>48.9519157409668</v>
       </c>
       <c r="C73" t="n">
         <v>61.3074836730957</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>53.26465225219727</v>
+        <v>53.26462936401367</v>
       </c>
       <c r="C74" t="n">
         <v>66.70874786376953</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>59.42050170898438</v>
+        <v>59.42051696777344</v>
       </c>
       <c r="C75" t="n">
         <v>74.41839599609375</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>57.30136489868164</v>
+        <v>57.30135345458984</v>
       </c>
       <c r="C76" t="n">
         <v>71.65914916992188</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>54.62628555297852</v>
+        <v>54.62629699707031</v>
       </c>
       <c r="C77" t="n">
         <v>68.31379699707031</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>48.12968444824219</v>
+        <v>48.12968063354492</v>
       </c>
       <c r="C78" t="n">
         <v>60.18936157226562</v>
@@ -2213,7 +2225,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>52.22511672973633</v>
+        <v>52.22512435913086</v>
       </c>
       <c r="C80" t="n">
         <v>65.19387054443359</v>
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>57.95023345947266</v>
+        <v>57.95026016235352</v>
       </c>
       <c r="C82" t="n">
         <v>72.23625183105469</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>53.31333160400391</v>
+        <v>53.31336212158203</v>
       </c>
       <c r="C83" t="n">
         <v>66.45626831054688</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>49.40707778930664</v>
+        <v>49.4070930480957</v>
       </c>
       <c r="C84" t="n">
         <v>61.58701324462891</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>49.53686904907227</v>
+        <v>49.536865234375</v>
       </c>
       <c r="C85" t="n">
         <v>61.63209915161133</v>
@@ -2416,7 +2428,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2445,7 +2457,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>51.37503814697266</v>
+        <v>51.37504196166992</v>
       </c>
       <c r="C88" t="n">
         <v>63.79621124267578</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>51.04828643798828</v>
+        <v>51.04826736450195</v>
       </c>
       <c r="C90" t="n">
         <v>63.39044189453125</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>50.22043991088867</v>
+        <v>50.22042846679688</v>
       </c>
       <c r="C91" t="n">
         <v>62.12804412841797</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>51.1461181640625</v>
+        <v>51.14613342285156</v>
       </c>
       <c r="C92" t="n">
         <v>63.27322006225586</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>54.15643310546875</v>
+        <v>54.15643692016602</v>
       </c>
       <c r="C93" t="n">
         <v>66.99729156494141</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>57.12237167358398</v>
+        <v>57.12238311767578</v>
       </c>
       <c r="C94" t="n">
         <v>70.43282318115234</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>59.36748504638672</v>
+        <v>59.36748886108398</v>
       </c>
       <c r="C95" t="n">
         <v>73.20108032226562</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>59.60150909423828</v>
+        <v>59.60149383544922</v>
       </c>
       <c r="C96" t="n">
         <v>73.48963165283203</v>
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>56.51770782470703</v>
+        <v>56.51773834228516</v>
       </c>
       <c r="C99" t="n">
         <v>69.46798706054688</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>57.3175048828125</v>
+        <v>57.31748962402344</v>
       </c>
       <c r="C100" t="n">
         <v>70.21640777587891</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>57.80329513549805</v>
+        <v>57.80329895019531</v>
       </c>
       <c r="C101" t="n">
         <v>70.81153869628906</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>60.26178359985352</v>
+        <v>60.26176071166992</v>
       </c>
       <c r="C102" t="n">
         <v>73.82326507568359</v>
@@ -2909,7 +2921,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>66.54290008544922</v>
+        <v>66.54290771484375</v>
       </c>
       <c r="C104" t="n">
         <v>81.04000091552734</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>70.96869659423828</v>
+        <v>70.96871185302734</v>
       </c>
       <c r="C105" t="n">
         <v>86.43000030517578</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>62.84018707275391</v>
+        <v>62.8402099609375</v>
       </c>
       <c r="C106" t="n">
         <v>76.09999847412109</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>59.98306274414062</v>
+        <v>59.98308563232422</v>
       </c>
       <c r="C107" t="n">
         <v>72.63999938964844</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>55.35884094238281</v>
+        <v>55.35886001586914</v>
       </c>
       <c r="C108" t="n">
         <v>67.04000091552734</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>54.48827743530273</v>
+        <v>54.48830032348633</v>
       </c>
       <c r="C109" t="n">
         <v>65.52999877929688</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>45.25863647460938</v>
+        <v>45.25861740112305</v>
       </c>
       <c r="C110" t="n">
         <v>54.43000030517578</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>45.19209671020508</v>
+        <v>45.19210433959961</v>
       </c>
       <c r="C111" t="n">
         <v>54.34999847412109</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.94748687744141</v>
+        <v>41.94750595092773</v>
       </c>
       <c r="C112" t="n">
         <v>49.9900016784668</v>
@@ -3199,7 +3211,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>40.90542984008789</v>
+        <v>40.90542602539062</v>
       </c>
       <c r="C115" t="n">
         <v>48.27999877929688</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>35.69482803344727</v>
+        <v>35.69481658935547</v>
       </c>
       <c r="C116" t="n">
         <v>42.13000106811523</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>35.86427688598633</v>
+        <v>35.86427307128906</v>
       </c>
       <c r="C117" t="n">
         <v>42.33000183105469</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>32.26449584960938</v>
+        <v>32.26450347900391</v>
       </c>
       <c r="C118" t="n">
         <v>37.65000152587891</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>32.25593566894531</v>
+        <v>32.25592803955078</v>
       </c>
       <c r="C119" t="n">
         <v>37.63999938964844</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.99884605407715</v>
+        <v>31.99884414672852</v>
       </c>
       <c r="C120" t="n">
         <v>37.34000015258789</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>29.05386543273926</v>
+        <v>29.05386734008789</v>
       </c>
       <c r="C121" t="n">
         <v>33.4900016784668</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>28.22970581054688</v>
+        <v>28.22970199584961</v>
       </c>
       <c r="C122" t="n">
         <v>32.54000091552734</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>25.39285469055176</v>
+        <v>25.39285850524902</v>
       </c>
       <c r="C123" t="n">
         <v>29.27000045776367</v>
@@ -3516,11 +3528,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>27.38028717041016</v>
+        <v>27.38028526306152</v>
       </c>
       <c r="C124" t="n">
         <v>31.10000038146973</v>
@@ -3543,11 +3555,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>31.72944068908691</v>
+        <v>31.72944641113281</v>
       </c>
       <c r="C125" t="n">
         <v>36.04000091552734</v>
@@ -3570,11 +3582,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>29.0090160369873</v>
+        <v>29.00902366638184</v>
       </c>
       <c r="C126" t="n">
         <v>32.95000076293945</v>
@@ -3597,7 +3609,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3624,11 +3636,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>28.52011489868164</v>
+        <v>28.52011680603027</v>
       </c>
       <c r="C128" t="n">
         <v>32.34999847412109</v>
@@ -3651,11 +3663,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.56924438476562</v>
+        <v>29.56923675537109</v>
       </c>
       <c r="C129" t="n">
         <v>33.54000091552734</v>
@@ -3678,11 +3690,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>32.43941116333008</v>
+        <v>32.43941497802734</v>
       </c>
       <c r="C130" t="n">
         <v>36.7400016784668</v>
@@ -3705,11 +3717,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>28.3425407409668</v>
+        <v>28.34254455566406</v>
       </c>
       <c r="C131" t="n">
         <v>32.09999847412109</v>
@@ -3732,11 +3744,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>33.03457260131836</v>
+        <v>33.03458404541016</v>
       </c>
       <c r="C132" t="n">
         <v>37.36000061035156</v>
@@ -3759,11 +3771,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>33.10531616210938</v>
+        <v>33.10530090332031</v>
       </c>
       <c r="C133" t="n">
         <v>37.43999862670898</v>
@@ -3786,11 +3798,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>33.43246078491211</v>
+        <v>33.43247222900391</v>
       </c>
       <c r="C134" t="n">
         <v>37.81000137329102</v>
@@ -3813,11 +3825,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>35.74030303955078</v>
+        <v>35.74029541015625</v>
       </c>
       <c r="C135" t="n">
         <v>40.41999816894531</v>
@@ -3840,11 +3852,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>35.49550247192383</v>
+        <v>35.49551391601562</v>
       </c>
       <c r="C136" t="n">
         <v>40.09000015258789</v>
@@ -3867,7 +3879,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3894,11 +3906,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>28.92587089538574</v>
+        <v>28.92587471008301</v>
       </c>
       <c r="C138" t="n">
         <v>32.66999816894531</v>
@@ -3921,11 +3933,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>29.20724105834961</v>
+        <v>29.20724678039551</v>
       </c>
       <c r="C139" t="n">
         <v>32.93999862670898</v>
@@ -3948,11 +3960,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>29.00330924987793</v>
+        <v>29.00330543518066</v>
       </c>
       <c r="C140" t="n">
         <v>32.70999908447266</v>
@@ -3975,11 +3987,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>27.1944751739502</v>
+        <v>27.19447708129883</v>
       </c>
       <c r="C141" t="n">
         <v>30.67000007629395</v>
@@ -4002,11 +4014,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>31.72797584533691</v>
+        <v>31.72796058654785</v>
       </c>
       <c r="C142" t="n">
         <v>35.72999954223633</v>
@@ -4029,11 +4041,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>30.36045074462891</v>
+        <v>30.36044311523438</v>
       </c>
       <c r="C143" t="n">
         <v>34.18999862670898</v>
@@ -4056,11 +4068,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>29.79214286804199</v>
+        <v>29.79214859008789</v>
       </c>
       <c r="C144" t="n">
         <v>33.54999923706055</v>
@@ -4083,11 +4095,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>32.03445816040039</v>
+        <v>32.03444290161133</v>
       </c>
       <c r="C145" t="n">
         <v>36.02000045776367</v>
@@ -4110,11 +4122,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>32.62141799926758</v>
+        <v>32.62142562866211</v>
       </c>
       <c r="C146" t="n">
         <v>36.68000030517578</v>
@@ -4137,11 +4149,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>31.20735168457031</v>
+        <v>31.20735740661621</v>
       </c>
       <c r="C147" t="n">
         <v>35.09000015258789</v>
@@ -4164,11 +4176,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>32.78087997436523</v>
+        <v>32.78086090087891</v>
       </c>
       <c r="C148" t="n">
         <v>36.81000137329102</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>34.43727111816406</v>
+        <v>34.43727874755859</v>
       </c>
       <c r="C149" t="n">
         <v>38.66999816894531</v>
@@ -4218,11 +4230,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>36.88625717163086</v>
+        <v>36.88626098632812</v>
       </c>
       <c r="C150" t="n">
         <v>41.41999816894531</v>
@@ -4245,7 +4257,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>43.34941864013672</v>
+        <v>43.34943008422852</v>
       </c>
       <c r="C152" t="n">
         <v>48.61999893188477</v>
@@ -4299,11 +4311,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>41.96743392944336</v>
+        <v>41.96744537353516</v>
       </c>
       <c r="C153" t="n">
         <v>47.06999969482422</v>
@@ -4326,11 +4338,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>38.45293045043945</v>
+        <v>38.45293807983398</v>
       </c>
       <c r="C154" t="n">
         <v>43.08000183105469</v>
@@ -4353,11 +4365,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>32.84744644165039</v>
+        <v>32.84745025634766</v>
       </c>
       <c r="C155" t="n">
         <v>36.79999923706055</v>
@@ -4380,11 +4392,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>28.66118621826172</v>
+        <v>28.66118049621582</v>
       </c>
       <c r="C156" t="n">
         <v>32.11000061035156</v>
@@ -4407,11 +4419,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>22.97592544555664</v>
+        <v>22.97592163085938</v>
       </c>
       <c r="C157" t="n">
         <v>25.70000076293945</v>
@@ -4434,7 +4446,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4461,11 +4473,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>25.15729141235352</v>
+        <v>25.15729331970215</v>
       </c>
       <c r="C159" t="n">
         <v>28.13999938964844</v>
@@ -4488,11 +4500,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>23.86030387878418</v>
+        <v>23.86030769348145</v>
       </c>
       <c r="C160" t="n">
         <v>26.63999938964844</v>
@@ -4515,11 +4527,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>23.4124813079834</v>
+        <v>23.41248512268066</v>
       </c>
       <c r="C161" t="n">
         <v>26.13999938964844</v>
@@ -4542,11 +4554,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>18.67445182800293</v>
+        <v>18.67445373535156</v>
       </c>
       <c r="C162" t="n">
         <v>20.85000038146973</v>
@@ -4569,7 +4581,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4596,11 +4608,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>21.38661766052246</v>
+        <v>21.3866138458252</v>
       </c>
       <c r="C164" t="n">
         <v>23.81999969482422</v>
@@ -4623,11 +4635,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>18.34292793273926</v>
+        <v>18.34292602539062</v>
       </c>
       <c r="C165" t="n">
         <v>20.43000030517578</v>
@@ -4650,11 +4662,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>19.07394409179688</v>
+        <v>19.07393455505371</v>
       </c>
       <c r="C166" t="n">
         <v>21.20000076293945</v>
@@ -4677,7 +4689,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4704,11 +4716,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>20.28854751586914</v>
+        <v>20.28855323791504</v>
       </c>
       <c r="C168" t="n">
         <v>22.54999923706055</v>
@@ -4731,11 +4743,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>22.58747863769531</v>
+        <v>22.58748245239258</v>
       </c>
       <c r="C169" t="n">
         <v>25.04999923706055</v>
@@ -4756,11 +4768,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>18.58395576477051</v>
+        <v>18.58395004272461</v>
       </c>
       <c r="C170" t="n">
         <v>20.61000061035156</v>
@@ -4781,7 +4793,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4806,11 +4818,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>8.906160354614258</v>
+        <v>8.906159400939941</v>
       </c>
       <c r="C172" t="n">
         <v>9.829999923706055</v>
@@ -4831,7 +4843,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4856,7 +4868,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>11.09872531890869</v>
+        <v>11.09872341156006</v>
       </c>
       <c r="C175" t="n">
         <v>12.25</v>
@@ -4906,11 +4918,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>10.42827224731445</v>
+        <v>10.42827320098877</v>
       </c>
       <c r="C176" t="n">
         <v>11.51000022888184</v>
@@ -4933,7 +4945,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4960,7 +4972,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -4987,7 +4999,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>11.10778617858887</v>
+        <v>11.1077880859375</v>
       </c>
       <c r="C180" t="n">
         <v>12.26000022888184</v>
@@ -5041,11 +5053,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>12.43962955474854</v>
+        <v>12.43963050842285</v>
       </c>
       <c r="C181" t="n">
         <v>13.72999954223633</v>
@@ -5068,11 +5080,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>11.21650695800781</v>
+        <v>11.21650886535645</v>
       </c>
       <c r="C182" t="n">
         <v>12.38000011444092</v>
@@ -5095,11 +5107,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>13.68087863922119</v>
+        <v>13.68087577819824</v>
       </c>
       <c r="C183" t="n">
         <v>15.10000038146973</v>
@@ -5122,11 +5134,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>12.43057346343994</v>
+        <v>12.43057155609131</v>
       </c>
       <c r="C184" t="n">
         <v>13.72000026702881</v>
@@ -5149,11 +5161,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>13.54497241973877</v>
+        <v>13.54497623443604</v>
       </c>
       <c r="C185" t="n">
         <v>14.94999980926514</v>
@@ -5176,11 +5188,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>14.60501766204834</v>
+        <v>14.60501480102539</v>
       </c>
       <c r="C186" t="n">
         <v>16.1200008392334</v>
@@ -5203,11 +5215,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>13.88019847869873</v>
+        <v>13.88020038604736</v>
       </c>
       <c r="C187" t="n">
         <v>15.31999969482422</v>
@@ -5230,11 +5242,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>12.51211547851562</v>
+        <v>12.51211357116699</v>
       </c>
       <c r="C188" t="n">
         <v>13.8100004196167</v>
@@ -5257,11 +5269,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>11.93226337432861</v>
+        <v>11.9322624206543</v>
       </c>
       <c r="C189" t="n">
         <v>13.17000007629395</v>
@@ -5284,7 +5296,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5311,11 +5323,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>12.70237827301025</v>
+        <v>12.70238018035889</v>
       </c>
       <c r="C191" t="n">
         <v>14.02000045776367</v>
@@ -5338,11 +5350,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>10.79973983764648</v>
+        <v>10.79973793029785</v>
       </c>
       <c r="C192" t="n">
         <v>11.92000007629395</v>
@@ -5365,7 +5377,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5392,11 +5404,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>14.94050693511963</v>
+        <v>14.94050598144531</v>
       </c>
       <c r="C194" t="n">
         <v>16.42000007629395</v>
@@ -5419,11 +5431,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>15.60473346710205</v>
+        <v>15.6047306060791</v>
       </c>
       <c r="C195" t="n">
         <v>17.14999961853027</v>
@@ -5446,11 +5458,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>17.88537788391113</v>
+        <v>17.8853816986084</v>
       </c>
       <c r="C196" t="n">
         <v>19.61000061035156</v>
@@ -5473,11 +5485,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>16.53553581237793</v>
+        <v>16.5355396270752</v>
       </c>
       <c r="C197" t="n">
         <v>18.1299991607666</v>
@@ -5500,11 +5512,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>18.24107933044434</v>
+        <v>18.24107551574707</v>
       </c>
       <c r="C198" t="n">
         <v>20</v>
@@ -5527,11 +5539,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>15.45918941497803</v>
+        <v>15.45919132232666</v>
       </c>
       <c r="C199" t="n">
         <v>16.90999984741211</v>
@@ -5554,7 +5566,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5581,11 +5593,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>16.15398788452148</v>
+        <v>16.15399360656738</v>
       </c>
       <c r="C201" t="n">
         <v>17.67000007629395</v>
@@ -5608,7 +5620,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5635,7 +5647,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5664,11 +5676,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>20.59037399291992</v>
+        <v>20.59037971496582</v>
       </c>
       <c r="C204" t="n">
         <v>22.45999908447266</v>
@@ -5693,11 +5705,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>19.19828224182129</v>
+        <v>19.19828414916992</v>
       </c>
       <c r="C205" t="n">
         <v>20.88999938964844</v>
@@ -5722,7 +5734,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>20.10811042785645</v>
+        <v>20.10811424255371</v>
       </c>
       <c r="C207" t="n">
         <v>21.8799991607666</v>
@@ -5780,7 +5792,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5809,11 +5821,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>15.43633365631104</v>
+        <v>15.43633556365967</v>
       </c>
       <c r="C209" t="n">
         <v>16.75</v>
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>12.96652126312256</v>
+        <v>12.96652030944824</v>
       </c>
       <c r="C210" t="n">
         <v>14.06999969482422</v>
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>14.83007431030273</v>
+        <v>14.83007621765137</v>
       </c>
       <c r="C211" t="n">
         <v>16.04000091552734</v>
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>18.5653247833252</v>
+        <v>18.56532859802246</v>
       </c>
       <c r="C212" t="n">
         <v>20.07999992370605</v>
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>19.5361270904541</v>
+        <v>19.53612518310547</v>
       </c>
       <c r="C213" t="n">
         <v>21.1299991607666</v>
@@ -5954,11 +5966,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>19.3708324432373</v>
+        <v>19.3708381652832</v>
       </c>
       <c r="C214" t="n">
         <v>20.89999961853027</v>
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>18.49961280822754</v>
+        <v>18.49961090087891</v>
       </c>
       <c r="C215" t="n">
         <v>19.95999908447266</v>
@@ -6012,11 +6024,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>17.44301986694336</v>
+        <v>17.44302177429199</v>
       </c>
       <c r="C216" t="n">
         <v>18.81999969482422</v>
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>18.84747314453125</v>
+        <v>18.84747505187988</v>
       </c>
       <c r="C217" t="n">
         <v>20.28000068664551</v>
@@ -6070,7 +6082,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>15.70622539520264</v>
+        <v>15.70622444152832</v>
       </c>
       <c r="C219" t="n">
         <v>16.89999961853027</v>
@@ -6128,7 +6140,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6157,11 +6169,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>17.2320728302002</v>
+        <v>17.23207092285156</v>
       </c>
       <c r="C221" t="n">
         <v>18.48999977111816</v>
@@ -6186,11 +6198,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>17.53962326049805</v>
+        <v>17.53962516784668</v>
       </c>
       <c r="C222" t="n">
         <v>18.81999969482422</v>
@@ -6215,7 +6227,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6244,7 +6256,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6273,11 +6285,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>16.6307430267334</v>
+        <v>16.63073921203613</v>
       </c>
       <c r="C225" t="n">
         <v>17.77000045776367</v>
@@ -6302,7 +6314,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6331,11 +6343,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>14.5839958190918</v>
+        <v>14.58399391174316</v>
       </c>
       <c r="C227" t="n">
         <v>15.51000022888184</v>
@@ -6360,11 +6372,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>15.0635461807251</v>
+        <v>15.06354522705078</v>
       </c>
       <c r="C228" t="n">
         <v>16.02000045776367</v>
@@ -6389,11 +6401,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>13.79447364807129</v>
+        <v>13.79447555541992</v>
       </c>
       <c r="C229" t="n">
         <v>14.60000038146973</v>
@@ -6418,11 +6430,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>13.65274906158447</v>
+        <v>13.65275096893311</v>
       </c>
       <c r="C230" t="n">
         <v>14.44999980926514</v>
@@ -6447,11 +6459,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>14.0968189239502</v>
+        <v>14.09681987762451</v>
       </c>
       <c r="C231" t="n">
         <v>14.92000007629395</v>
@@ -6476,11 +6488,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>14.45777320861816</v>
+        <v>14.4577751159668</v>
       </c>
       <c r="C232" t="n">
         <v>15.22000026702881</v>
@@ -6505,7 +6517,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6534,7 +6546,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6563,7 +6575,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6592,11 +6604,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>12.2313985824585</v>
+        <v>12.23139762878418</v>
       </c>
       <c r="C236" t="n">
         <v>12.57999992370605</v>
@@ -6621,7 +6633,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6650,11 +6662,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>12.95583534240723</v>
+        <v>12.95583724975586</v>
       </c>
       <c r="C238" t="n">
         <v>13.25</v>
@@ -6679,7 +6691,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6708,11 +6720,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>15.01899242401123</v>
+        <v>15.01899147033691</v>
       </c>
       <c r="C240" t="n">
         <v>15.35999965667725</v>
@@ -6737,7 +6749,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6766,11 +6778,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>18.02555084228516</v>
+        <v>18.02555274963379</v>
       </c>
       <c r="C242" t="n">
         <v>18.35000038146973</v>
@@ -6795,7 +6807,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6853,7 +6865,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6882,7 +6894,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -6998,32 +7010,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>20.28000068664551</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="C250" t="n">
-        <v>20.28000068664551</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="D250" t="n">
-        <v>47971700</v>
+        <v>51259400</v>
       </c>
       <c r="E250" t="n">
         <v>0.2700000000000009</v>
       </c>
       <c r="F250" t="n">
-        <v>75.11111365424237</v>
+        <v>73.70370229085262</v>
       </c>
       <c r="G250" t="n">
         <v>358888480</v>
       </c>
       <c r="H250" t="n">
-        <v>7278258620.829163</v>
+        <v>7141880615.09491</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1336674278316206</v>
+        <v>0.1428282122624833</v>
       </c>
     </row>
   </sheetData>
@@ -7055,75 +7067,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7159,13 +7171,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7201,13 +7213,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7243,13 +7255,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7285,13 +7297,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7360,7 +7372,7 @@
       <c r="I7" t="n">
         <v>3.174030658250676</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K7" t="n">
@@ -7373,13 +7385,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7406,7 +7418,7 @@
       <c r="I8" t="n">
         <v>3.065825067628494</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K8" t="n">
@@ -7419,13 +7431,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7452,7 +7464,7 @@
       <c r="I9" t="n">
         <v>3.45356176735798</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K9" t="n">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7498,7 +7510,7 @@
       <c r="I10" t="n">
         <v>3.489630297565374</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K10" t="n">
@@ -7511,13 +7523,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7544,7 +7556,7 @@
       <c r="I11" t="n">
         <v>3.588818755635708</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K11" t="n">
@@ -7557,13 +7569,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7590,7 +7602,7 @@
       <c r="I12" t="n">
         <v>3.543733092876465</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7603,13 +7615,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7636,7 +7648,7 @@
       <c r="I13" t="n">
         <v>3.69702434625789</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7649,13 +7661,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7682,7 +7694,7 @@
       <c r="I14" t="n">
         <v>3.958521190261497</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7695,13 +7707,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7728,7 +7740,7 @@
       <c r="I15" t="n">
         <v>4.229035166816952</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K15" t="n">
@@ -7741,13 +7753,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7774,7 +7786,7 @@
       <c r="I16" t="n">
         <v>4.643823264201984</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K16" t="n">
@@ -7787,13 +7799,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7820,7 +7832,7 @@
       <c r="I17" t="n">
         <v>4.905320108205591</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K17" t="n">
@@ -7833,13 +7845,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7866,7 +7878,7 @@
       <c r="I18" t="n">
         <v>5.067628494138864</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -7879,13 +7891,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7912,7 +7924,7 @@
       <c r="I19" t="n">
         <v>5.256988277727683</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -7925,13 +7937,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7958,7 +7970,7 @@
       <c r="I20" t="n">
         <v>5.031559963931469</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K20" t="n">
@@ -7971,13 +7983,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8004,7 +8016,7 @@
       <c r="I21" t="n">
         <v>4.869251577998197</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="K21" t="n">
@@ -8017,13 +8029,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8050,7 +8062,7 @@
       <c r="I22" t="n">
         <v>4.923354373309288</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="K22" t="n">
@@ -8063,13 +8075,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8096,7 +8108,7 @@
       <c r="I23" t="n">
         <v>4.896302975653742</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K23" t="n">
@@ -8109,13 +8121,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8142,7 +8154,7 @@
       <c r="I24" t="n">
         <v>5.076645626690713</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="K24" t="n">
@@ -8155,13 +8167,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41731</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8188,7 +8200,7 @@
       <c r="I25" t="n">
         <v>5.398521190261498</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="K25" t="n">
@@ -8201,13 +8213,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8234,7 +8246,7 @@
       <c r="I26" t="n">
         <v>5.67496844003607</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K26" t="n">
@@ -8247,13 +8259,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8280,7 +8292,7 @@
       <c r="I27" t="n">
         <v>5.685347159603246</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="K27" t="n">
@@ -8293,13 +8305,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8326,7 +8338,7 @@
       <c r="I28" t="n">
         <v>5.21</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="K28" t="n">
@@ -8339,13 +8351,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8372,7 +8384,7 @@
       <c r="I29" t="n">
         <v>4.51</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K29" t="n">
@@ -8385,13 +8397,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8418,7 +8430,7 @@
       <c r="I30" t="n">
         <v>3.3</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K30" t="n">
@@ -8431,13 +8443,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8464,7 +8476,7 @@
       <c r="I31" t="n">
         <v>-2.149999999999999</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K31" t="n">
@@ -8477,13 +8489,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8510,7 +8522,7 @@
       <c r="I32" t="n">
         <v>-3.229999999999999</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K32" t="n">
@@ -8523,13 +8535,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8556,7 +8568,7 @@
       <c r="I33" t="n">
         <v>-4.549999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K33" t="n">
@@ -8569,13 +8581,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8602,7 +8614,7 @@
       <c r="I34" t="n">
         <v>-8.58</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K34" t="n">
@@ -8615,13 +8627,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8648,7 +8660,7 @@
       <c r="I35" t="n">
         <v>-6.42</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K35" t="n">
@@ -8661,13 +8673,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8694,7 +8706,7 @@
       <c r="I36" t="n">
         <v>-6.42</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K36" t="n">
@@ -8707,13 +8719,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8740,7 +8752,7 @@
       <c r="I37" t="n">
         <v>-6.039999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K37" t="n">
@@ -8753,13 +8765,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8786,7 +8798,7 @@
       <c r="I38" t="n">
         <v>-2.49</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K38" t="n">
@@ -8799,13 +8811,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8832,7 +8844,7 @@
       <c r="I39" t="n">
         <v>-0.63</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K39" t="n">
@@ -8845,13 +8857,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8878,7 +8890,7 @@
       <c r="I40" t="n">
         <v>-0.49</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K40" t="n">
@@ -8891,13 +8903,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8924,7 +8936,7 @@
       <c r="I41" t="n">
         <v>-0.23</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K41" t="n">
@@ -8937,13 +8949,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8970,7 +8982,7 @@
       <c r="I42" t="n">
         <v>-0.16</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K42" t="n">
@@ -8983,13 +8995,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9016,7 +9028,7 @@
       <c r="I43" t="n">
         <v>-0.09</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="K43" t="n">
@@ -9029,13 +9041,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9062,7 +9074,7 @@
       <c r="I44" t="n">
         <v>-0.11</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K44" t="n">
@@ -9075,13 +9087,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9159,13 +9171,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9201,13 +9213,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9234,7 +9246,7 @@
       <c r="I48" t="n">
         <v>-7.23</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="K48" t="n">
@@ -9247,13 +9259,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9280,7 +9292,7 @@
       <c r="I49" t="n">
         <v>-6.73</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="K49" t="n">
@@ -9293,13 +9305,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9326,7 +9338,7 @@
       <c r="I50" t="n">
         <v>-6.619999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K50" t="n">
@@ -9339,13 +9351,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9372,7 +9384,7 @@
       <c r="I51" t="n">
         <v>-1.579999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K51" t="n">
@@ -9385,13 +9397,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9418,7 +9430,7 @@
       <c r="I52" t="n">
         <v>-1.409999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K52" t="n">
@@ -9431,13 +9443,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9464,7 +9476,7 @@
       <c r="I53" t="n">
         <v>-1.45</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K53" t="n">
@@ -9477,13 +9489,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9510,7 +9522,7 @@
       <c r="I54" t="n">
         <v>-0.649999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K54" t="n">
@@ -9523,13 +9535,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9556,7 +9568,7 @@
       <c r="I55" t="n">
         <v>-0.4799999999999991</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K55" t="n">
@@ -9569,13 +9581,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9602,7 +9614,7 @@
       <c r="I56" t="n">
         <v>-0.2299999999999991</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K56" t="n">
@@ -9615,13 +9627,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9648,7 +9660,7 @@
       <c r="I57" t="n">
         <v>0.0300000000000009</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K57" t="n">
@@ -9661,13 +9673,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9694,7 +9706,7 @@
       <c r="I58" t="n">
         <v>0.3900000000000009</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K58" t="n">
@@ -9707,13 +9719,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9740,7 +9752,7 @@
       <c r="I59" t="n">
         <v>0.840000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K59" t="n">
@@ -9753,13 +9765,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9786,7 +9798,7 @@
       <c r="I60" t="n">
         <v>1.050000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K60" t="n">
@@ -9799,13 +9811,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9832,7 +9844,7 @@
       <c r="I61" t="n">
         <v>1.260000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K61" t="n">
@@ -9845,13 +9857,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9878,7 +9890,7 @@
       <c r="I62" t="n">
         <v>2.500000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="K62" t="n">
@@ -9891,13 +9903,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9924,7 +9936,7 @@
       <c r="I63" t="n">
         <v>2.480000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K63" t="n">
@@ -9937,13 +9949,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9970,7 +9982,7 @@
       <c r="I64" t="n">
         <v>2.660000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="K64" t="n">
@@ -9983,13 +9995,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10016,7 +10028,7 @@
       <c r="I65" t="n">
         <v>2.700000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="K65" t="n">
@@ -10029,13 +10041,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10062,7 +10074,7 @@
       <c r="I66" t="n">
         <v>1.600000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K66" t="n">
@@ -10075,13 +10087,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10108,7 +10120,7 @@
       <c r="I67" t="n">
         <v>1.490000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K67" t="n">
@@ -10121,13 +10133,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10154,7 +10166,7 @@
       <c r="I68" t="n">
         <v>1.210000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="K68" t="n">
@@ -10167,13 +10179,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10200,7 +10212,7 @@
       <c r="I69" t="n">
         <v>0.990000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="K69" t="n">
@@ -10213,13 +10225,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10246,7 +10258,7 @@
       <c r="I70" t="n">
         <v>0.390000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K70" t="n">
@@ -10259,13 +10271,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10292,7 +10304,7 @@
       <c r="I71" t="n">
         <v>0.2500000000000009</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K71" t="n">
@@ -10305,13 +10317,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10332,7 +10344,7 @@
       <c r="I72" t="n">
         <v>0.2700000000000009</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K72" t="n">
@@ -10369,52 +10381,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40028</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10443,10 +10455,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40119</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10475,10 +10487,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40225</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10507,10 +10519,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40301</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10539,10 +10551,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40392</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10571,10 +10583,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10603,10 +10615,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40591</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="C8" t="n">
@@ -10635,10 +10647,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40665</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10667,10 +10679,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10699,10 +10711,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10731,10 +10743,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C12" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41031</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C13" t="n">
@@ -10795,10 +10807,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41123</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C14" t="n">
@@ -10827,10 +10839,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41212</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -10859,10 +10871,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41319</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C17" t="n">
@@ -10923,10 +10935,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="C18" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="C19" t="n">
@@ -10987,10 +10999,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41677</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C20" t="n">
@@ -11019,10 +11031,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="C21" t="n">
@@ -11051,10 +11063,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="C22" t="n">
@@ -11083,10 +11095,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41942</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C23" t="n">
@@ -11115,10 +11127,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42047</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="C24" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="C25" t="n">
@@ -11179,10 +11191,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42219</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11211,10 +11223,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42305</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C27" t="n">
@@ -11243,10 +11255,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C28" t="n">
@@ -11275,10 +11287,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42488</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C29" t="n">
@@ -11307,10 +11319,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11339,10 +11351,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C31" t="n">
@@ -11371,10 +11383,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C32" t="n">
@@ -11403,10 +11415,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C33" t="n">
@@ -11435,10 +11447,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11467,10 +11479,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11499,10 +11511,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C36" t="n">
@@ -11531,10 +11543,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11563,10 +11575,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11595,10 +11607,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11627,10 +11639,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="C40" t="n">
@@ -11659,10 +11671,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11691,10 +11703,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -11723,10 +11735,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C43" t="n">
@@ -11755,10 +11767,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43868</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C44" t="n">
@@ -11787,10 +11799,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43938</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C45" t="n">
@@ -11819,10 +11831,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="C46" t="n">
@@ -11851,10 +11863,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44130</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="C47" t="n">
@@ -11883,10 +11895,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44232</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C48" t="n">
@@ -11915,10 +11927,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C49" t="n">
@@ -11947,10 +11959,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -11979,10 +11991,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44484</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C51" t="n">
@@ -12011,10 +12023,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44596</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C52" t="n">
@@ -12043,10 +12055,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44666</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12075,10 +12087,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44757</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C54" t="n">
@@ -12107,10 +12119,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44848</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12139,10 +12151,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C56" t="n">
@@ -12171,10 +12183,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45030</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12203,10 +12215,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45121</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C58" t="n">
@@ -12235,10 +12247,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45212</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C59" t="n">
@@ -12267,10 +12279,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="C60" t="n">
@@ -12299,10 +12311,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45394</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C61" t="n">
@@ -12331,10 +12343,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45485</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="C62" t="n">
@@ -12363,10 +12375,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45576</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="C63" t="n">
@@ -12395,10 +12407,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C64" t="n">
@@ -12427,10 +12439,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C65" t="n">
@@ -12459,10 +12471,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="C66" t="n">
@@ -12491,10 +12503,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="C67" t="n">
@@ -12523,10 +12535,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C68" t="n">
@@ -12555,10 +12567,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C69" t="n">
@@ -12605,12 +12617,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/NOV.xlsx
+++ b/salidas/empresas/NOV.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.26827049255371</v>
+        <v>26.26827621459961</v>
       </c>
       <c r="C2" t="n">
         <v>34.29666519165039</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>21.02289962768555</v>
+        <v>21.02289772033691</v>
       </c>
       <c r="C3" t="n">
         <v>27.44815063476562</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.81652450561523</v>
+        <v>23.81651306152344</v>
       </c>
       <c r="C5" t="n">
         <v>31.0955810546875</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.81164360046387</v>
+        <v>22.81164932250977</v>
       </c>
       <c r="C6" t="n">
         <v>29.78358840942383</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.86548042297363</v>
+        <v>21.86547470092773</v>
       </c>
       <c r="C7" t="n">
         <v>28.54824256896973</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>23.15005493164062</v>
+        <v>23.15005874633789</v>
       </c>
       <c r="C8" t="n">
         <v>30.22542762756348</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>22.54920768737793</v>
+        <v>22.5492000579834</v>
       </c>
       <c r="C9" t="n">
         <v>29.44093894958496</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.21831321716309</v>
+        <v>20.21830749511719</v>
       </c>
       <c r="C10" t="n">
         <v>26.39765548706055</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.85714530944824</v>
+        <v>20.85714912414551</v>
       </c>
       <c r="C11" t="n">
         <v>27.23174095153809</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>22.96703720092773</v>
+        <v>22.96703338623047</v>
       </c>
       <c r="C12" t="n">
         <v>29.98647308349609</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>21.12649917602539</v>
+        <v>21.12650489807129</v>
       </c>
       <c r="C13" t="n">
         <v>27.58340835571289</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>20.94002532958984</v>
+        <v>20.94002914428711</v>
       </c>
       <c r="C14" t="n">
         <v>27.33994674682617</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>24.04788398742676</v>
+        <v>24.04787445068359</v>
       </c>
       <c r="C15" t="n">
         <v>31.39765548706055</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>26.8621997833252</v>
+        <v>26.86220169067383</v>
       </c>
       <c r="C16" t="n">
         <v>35.07213592529297</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>29.30014419555664</v>
+        <v>29.30014610290527</v>
       </c>
       <c r="C17" t="n">
         <v>38.25518417358398</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>35.995849609375</v>
+        <v>35.99585342407227</v>
       </c>
       <c r="C19" t="n">
         <v>46.99729537963867</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>41.47603607177734</v>
+        <v>41.47602462768555</v>
       </c>
       <c r="C20" t="n">
         <v>54.15238952636719</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>44.20056915283203</v>
+        <v>44.20058822631836</v>
       </c>
       <c r="C21" t="n">
         <v>57.70964813232422</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>49.8983039855957</v>
+        <v>49.89830017089844</v>
       </c>
       <c r="C22" t="n">
         <v>65.14878082275391</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>47.06669998168945</v>
+        <v>47.06670379638672</v>
       </c>
       <c r="C24" t="n">
         <v>61.45175933837891</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>50.73396301269531</v>
+        <v>50.73397445678711</v>
       </c>
       <c r="C25" t="n">
         <v>66.23985290527344</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>41.57617950439453</v>
+        <v>41.57617568969727</v>
       </c>
       <c r="C26" t="n">
         <v>54.28313827514648</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>43.02650451660156</v>
+        <v>43.02650833129883</v>
       </c>
       <c r="C27" t="n">
         <v>56.17673492431641</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>47.27390289306641</v>
+        <v>47.27389526367188</v>
       </c>
       <c r="C29" t="n">
         <v>61.72227096557617</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>57.54360580444336</v>
+        <v>57.54361343383789</v>
       </c>
       <c r="C30" t="n">
         <v>75.13074493408203</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>61.27305603027344</v>
+        <v>61.27309417724609</v>
       </c>
       <c r="C31" t="n">
         <v>80</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>54.30455780029297</v>
+        <v>54.3045539855957</v>
       </c>
       <c r="C32" t="n">
         <v>70.90171051025391</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>50.92044448852539</v>
+        <v>50.92046356201172</v>
       </c>
       <c r="C33" t="n">
         <v>66.48331451416016</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>34.69054412841797</v>
+        <v>34.69054794311523</v>
       </c>
       <c r="C34" t="n">
         <v>45.29305648803711</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.64305686950684</v>
+        <v>20.64304542541504</v>
       </c>
       <c r="C35" t="n">
         <v>26.95220947265625</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>19.53803443908691</v>
+        <v>19.53803253173828</v>
       </c>
       <c r="C36" t="n">
         <v>25.50946807861328</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>18.26036262512207</v>
+        <v>18.2603645324707</v>
       </c>
       <c r="C38" t="n">
         <v>23.8412971496582</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>18.46064376831055</v>
+        <v>18.46065139770508</v>
       </c>
       <c r="C39" t="n">
         <v>24.1027946472168</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.91240119934082</v>
+        <v>20.91239738464355</v>
       </c>
       <c r="C41" t="n">
         <v>27.30387687683105</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>26.67228507995605</v>
+        <v>26.67228126525879</v>
       </c>
       <c r="C42" t="n">
         <v>34.82416534423828</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>22.55610656738281</v>
+        <v>22.55610847473145</v>
       </c>
       <c r="C43" t="n">
         <v>29.44995498657227</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>24.82139015197754</v>
+        <v>24.82138633728027</v>
       </c>
       <c r="C44" t="n">
         <v>32.40757369995117</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>25.10455894470215</v>
+        <v>25.10455322265625</v>
       </c>
       <c r="C45" t="n">
         <v>32.77727890014648</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>29.78705406188965</v>
+        <v>29.78704643249512</v>
       </c>
       <c r="C46" t="n">
         <v>38.89089202880859</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>30.48553657531738</v>
+        <v>30.48554420471191</v>
       </c>
       <c r="C48" t="n">
         <v>38.79170227050781</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.98322105407715</v>
+        <v>28.98322677612305</v>
       </c>
       <c r="C50" t="n">
         <v>36.88007354736328</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>30.80442810058594</v>
+        <v>30.80442428588867</v>
       </c>
       <c r="C51" t="n">
         <v>39.19747543334961</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>28.82280158996582</v>
+        <v>28.82281112670898</v>
       </c>
       <c r="C52" t="n">
         <v>36.59152221679688</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>31.27325439453125</v>
+        <v>31.27325057983398</v>
       </c>
       <c r="C53" t="n">
         <v>39.70243453979492</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>27.08266067504883</v>
+        <v>27.08264923095703</v>
       </c>
       <c r="C54" t="n">
         <v>34.38232421875</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>23.55521583557129</v>
+        <v>23.55521774291992</v>
       </c>
       <c r="C55" t="n">
         <v>29.81965637207031</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>27.89302444458008</v>
+        <v>27.89302825927734</v>
       </c>
       <c r="C56" t="n">
         <v>35.31109237670898</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>26.80322265625</v>
+        <v>26.80322647094727</v>
       </c>
       <c r="C57" t="n">
         <v>33.93146896362305</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>31.75553703308105</v>
+        <v>31.75554275512695</v>
       </c>
       <c r="C58" t="n">
         <v>40.09918975830078</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>38.38942337036133</v>
+        <v>38.38943099975586</v>
       </c>
       <c r="C59" t="n">
         <v>48.47610473632812</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>43.76651382446289</v>
+        <v>43.76650619506836</v>
       </c>
       <c r="C60" t="n">
         <v>55.26600646972656</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>48.10882949829102</v>
+        <v>48.10882568359375</v>
       </c>
       <c r="C61" t="n">
         <v>60.64021682739258</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>56.92222595214844</v>
+        <v>56.92224502563477</v>
       </c>
       <c r="C63" t="n">
         <v>71.74932098388672</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>56.78586959838867</v>
+        <v>56.78585433959961</v>
       </c>
       <c r="C64" t="n">
         <v>71.47881317138672</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>51.99342346191406</v>
+        <v>51.99343109130859</v>
       </c>
       <c r="C66" t="n">
         <v>65.44635009765625</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>56.11320114135742</v>
+        <v>56.11319351196289</v>
       </c>
       <c r="C67" t="n">
         <v>70.52299499511719</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>47.43900680541992</v>
+        <v>47.43899917602539</v>
       </c>
       <c r="C69" t="n">
         <v>59.62128067016602</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>36.81230545043945</v>
+        <v>36.81230163574219</v>
       </c>
       <c r="C70" t="n">
         <v>46.18575286865234</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>51.26557159423828</v>
+        <v>51.26557540893555</v>
       </c>
       <c r="C71" t="n">
         <v>64.31920623779297</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>51.62305068969727</v>
+        <v>51.62306213378906</v>
       </c>
       <c r="C72" t="n">
         <v>64.65283966064453</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>48.9519157409668</v>
+        <v>48.95190048217773</v>
       </c>
       <c r="C73" t="n">
         <v>61.3074836730957</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>53.26462936401367</v>
+        <v>53.26464080810547</v>
       </c>
       <c r="C74" t="n">
         <v>66.70874786376953</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>59.42051696777344</v>
+        <v>59.42052459716797</v>
       </c>
       <c r="C75" t="n">
         <v>74.41839599609375</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>57.30135345458984</v>
+        <v>57.30135726928711</v>
       </c>
       <c r="C76" t="n">
         <v>71.65914916992188</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>54.62629699707031</v>
+        <v>54.62629318237305</v>
       </c>
       <c r="C77" t="n">
         <v>68.31379699707031</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>46.54754257202148</v>
+        <v>46.54754638671875</v>
       </c>
       <c r="C79" t="n">
         <v>58.10640335083008</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>56.92033767700195</v>
+        <v>56.92035293579102</v>
       </c>
       <c r="C81" t="n">
         <v>71.05500793457031</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>53.31336212158203</v>
+        <v>53.3133659362793</v>
       </c>
       <c r="C83" t="n">
         <v>66.45626831054688</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>49.4070930480957</v>
+        <v>49.40709686279297</v>
       </c>
       <c r="C84" t="n">
         <v>61.58701324462891</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>49.536865234375</v>
+        <v>49.53688430786133</v>
       </c>
       <c r="C85" t="n">
         <v>61.63209915161133</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>53.73319625854492</v>
+        <v>53.73321914672852</v>
       </c>
       <c r="C86" t="n">
         <v>66.85301971435547</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>49.37743377685547</v>
+        <v>49.3774299621582</v>
       </c>
       <c r="C87" t="n">
         <v>61.43372344970703</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>51.37504196166992</v>
+        <v>51.37504577636719</v>
       </c>
       <c r="C88" t="n">
         <v>63.79621124267578</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>50.22042846679688</v>
+        <v>50.22042465209961</v>
       </c>
       <c r="C91" t="n">
         <v>62.12804412841797</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>51.14613342285156</v>
+        <v>51.14612197875977</v>
       </c>
       <c r="C92" t="n">
         <v>63.27322006225586</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>54.15643692016602</v>
+        <v>54.15641403198242</v>
       </c>
       <c r="C93" t="n">
         <v>66.99729156494141</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>57.12238311767578</v>
+        <v>57.12237167358398</v>
       </c>
       <c r="C94" t="n">
         <v>70.43282318115234</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>59.60149383544922</v>
+        <v>59.60152435302734</v>
       </c>
       <c r="C96" t="n">
         <v>73.48963165283203</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>58.34442901611328</v>
+        <v>58.34443664550781</v>
       </c>
       <c r="C97" t="n">
         <v>71.7132568359375</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>55.02850723266602</v>
+        <v>55.02849960327148</v>
       </c>
       <c r="C98" t="n">
         <v>67.63751220703125</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>57.80329895019531</v>
+        <v>57.80329513549805</v>
       </c>
       <c r="C101" t="n">
         <v>70.81153869628906</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>60.26176071166992</v>
+        <v>60.26177978515625</v>
       </c>
       <c r="C102" t="n">
         <v>73.82326507568359</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>67.61856079101562</v>
+        <v>67.61856842041016</v>
       </c>
       <c r="C103" t="n">
         <v>82.34999847412109</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>70.96871185302734</v>
+        <v>70.96868133544922</v>
       </c>
       <c r="C105" t="n">
         <v>86.43000030517578</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>62.8402099609375</v>
+        <v>62.84019470214844</v>
       </c>
       <c r="C106" t="n">
         <v>76.09999847412109</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>59.98308563232422</v>
+        <v>59.98309707641602</v>
       </c>
       <c r="C107" t="n">
         <v>72.63999938964844</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>55.35886001586914</v>
+        <v>55.35883712768555</v>
       </c>
       <c r="C108" t="n">
         <v>67.04000091552734</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>54.48830032348633</v>
+        <v>54.48828887939453</v>
       </c>
       <c r="C109" t="n">
         <v>65.52999877929688</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>45.25861740112305</v>
+        <v>45.25862503051758</v>
       </c>
       <c r="C110" t="n">
         <v>54.43000030517578</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>45.19210433959961</v>
+        <v>45.19210052490234</v>
       </c>
       <c r="C111" t="n">
         <v>54.34999847412109</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.94750595092773</v>
+        <v>41.94749450683594</v>
       </c>
       <c r="C112" t="n">
         <v>49.9900016784668</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>45.65639877319336</v>
+        <v>45.65638732910156</v>
       </c>
       <c r="C113" t="n">
         <v>54.40999984741211</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>41.27619934082031</v>
+        <v>41.27619552612305</v>
       </c>
       <c r="C114" t="n">
         <v>49.18999862670898</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>40.90542602539062</v>
+        <v>40.90543746948242</v>
       </c>
       <c r="C115" t="n">
         <v>48.27999877929688</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>35.86427307128906</v>
+        <v>35.8642692565918</v>
       </c>
       <c r="C117" t="n">
         <v>42.33000183105469</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>32.25592803955078</v>
+        <v>32.25591278076172</v>
       </c>
       <c r="C119" t="n">
         <v>37.63999938964844</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.99884414672852</v>
+        <v>31.99885749816895</v>
       </c>
       <c r="C120" t="n">
         <v>37.34000015258789</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>29.05386734008789</v>
+        <v>29.05386543273926</v>
       </c>
       <c r="C121" t="n">
         <v>33.4900016784668</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>28.22970199584961</v>
+        <v>28.22970390319824</v>
       </c>
       <c r="C122" t="n">
         <v>32.54000091552734</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>25.39285850524902</v>
+        <v>25.39285087585449</v>
       </c>
       <c r="C123" t="n">
         <v>29.27000045776367</v>
@@ -3532,7 +3532,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>27.38028526306152</v>
+        <v>27.38028907775879</v>
       </c>
       <c r="C124" t="n">
         <v>31.10000038146973</v>
@@ -3559,7 +3559,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>31.72944641113281</v>
+        <v>31.72943878173828</v>
       </c>
       <c r="C125" t="n">
         <v>36.04000091552734</v>
@@ -3586,7 +3586,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>29.00902366638184</v>
+        <v>29.00901031494141</v>
       </c>
       <c r="C126" t="n">
         <v>32.95000076293945</v>
@@ -3613,7 +3613,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>29.66621208190918</v>
+        <v>29.66621780395508</v>
       </c>
       <c r="C127" t="n">
         <v>33.65000152587891</v>
@@ -3694,7 +3694,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>32.43941497802734</v>
+        <v>32.43939971923828</v>
       </c>
       <c r="C130" t="n">
         <v>36.7400016784668</v>
@@ -3721,7 +3721,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>28.34254455566406</v>
+        <v>28.34253883361816</v>
       </c>
       <c r="C131" t="n">
         <v>32.09999847412109</v>
@@ -3748,7 +3748,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>33.03458404541016</v>
+        <v>33.03458023071289</v>
       </c>
       <c r="C132" t="n">
         <v>37.36000061035156</v>
@@ -3775,7 +3775,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>33.10530090332031</v>
+        <v>33.10531997680664</v>
       </c>
       <c r="C133" t="n">
         <v>37.43999862670898</v>
@@ -3802,7 +3802,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>33.43247222900391</v>
+        <v>33.43246459960938</v>
       </c>
       <c r="C134" t="n">
         <v>37.81000137329102</v>
@@ -3829,7 +3829,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>35.74029541015625</v>
+        <v>35.74028396606445</v>
       </c>
       <c r="C135" t="n">
         <v>40.41999816894531</v>
@@ -3856,7 +3856,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>35.49551391601562</v>
+        <v>35.49550628662109</v>
       </c>
       <c r="C136" t="n">
         <v>40.09000015258789</v>
@@ -3883,7 +3883,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>30.96228408813477</v>
+        <v>30.96229553222656</v>
       </c>
       <c r="C137" t="n">
         <v>34.97000122070312</v>
@@ -3910,7 +3910,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>28.92587471008301</v>
+        <v>28.92587089538574</v>
       </c>
       <c r="C138" t="n">
         <v>32.66999816894531</v>
@@ -3937,7 +3937,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>29.20724678039551</v>
+        <v>29.20725059509277</v>
       </c>
       <c r="C139" t="n">
         <v>32.93999862670898</v>
@@ -3964,7 +3964,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>29.00330543518066</v>
+        <v>29.0033073425293</v>
       </c>
       <c r="C140" t="n">
         <v>32.70999908447266</v>
@@ -3991,7 +3991,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>27.19447708129883</v>
+        <v>27.19448089599609</v>
       </c>
       <c r="C141" t="n">
         <v>30.67000007629395</v>
@@ -4018,7 +4018,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>31.72796058654785</v>
+        <v>31.72796821594238</v>
       </c>
       <c r="C142" t="n">
         <v>35.72999954223633</v>
@@ -4045,7 +4045,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>30.36044311523438</v>
+        <v>30.36045074462891</v>
       </c>
       <c r="C143" t="n">
         <v>34.18999862670898</v>
@@ -4072,7 +4072,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>29.79214859008789</v>
+        <v>29.79213523864746</v>
       </c>
       <c r="C144" t="n">
         <v>33.54999923706055</v>
@@ -4099,7 +4099,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>32.03444290161133</v>
+        <v>32.03445053100586</v>
       </c>
       <c r="C145" t="n">
         <v>36.02000045776367</v>
@@ -4126,7 +4126,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>32.62142562866211</v>
+        <v>32.62141036987305</v>
       </c>
       <c r="C146" t="n">
         <v>36.68000030517578</v>
@@ -4180,7 +4180,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>32.78086090087891</v>
+        <v>32.7808723449707</v>
       </c>
       <c r="C148" t="n">
         <v>36.81000137329102</v>
@@ -4207,7 +4207,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>34.43727874755859</v>
+        <v>34.43727493286133</v>
       </c>
       <c r="C149" t="n">
         <v>38.66999816894531</v>
@@ -4234,7 +4234,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>36.88626098632812</v>
+        <v>36.88626861572266</v>
       </c>
       <c r="C150" t="n">
         <v>41.41999816894531</v>
@@ -4288,7 +4288,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>43.34943008422852</v>
+        <v>43.34941101074219</v>
       </c>
       <c r="C152" t="n">
         <v>48.61999893188477</v>
@@ -4315,7 +4315,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>41.96744537353516</v>
+        <v>41.96744155883789</v>
       </c>
       <c r="C153" t="n">
         <v>47.06999969482422</v>
@@ -4342,7 +4342,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>38.45293807983398</v>
+        <v>38.45293426513672</v>
       </c>
       <c r="C154" t="n">
         <v>43.08000183105469</v>
@@ -4450,7 +4450,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>26.35525703430176</v>
+        <v>26.35525321960449</v>
       </c>
       <c r="C158" t="n">
         <v>29.47999954223633</v>
@@ -4477,7 +4477,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>25.15729331970215</v>
+        <v>25.15729522705078</v>
       </c>
       <c r="C159" t="n">
         <v>28.13999938964844</v>
@@ -4504,7 +4504,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>23.86030769348145</v>
+        <v>23.86030578613281</v>
       </c>
       <c r="C160" t="n">
         <v>26.63999938964844</v>
@@ -4531,7 +4531,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>23.41248512268066</v>
+        <v>23.41247940063477</v>
       </c>
       <c r="C161" t="n">
         <v>26.13999938964844</v>
@@ -4558,7 +4558,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>18.67445373535156</v>
+        <v>18.67445182800293</v>
       </c>
       <c r="C162" t="n">
         <v>20.85000038146973</v>
@@ -4585,7 +4585,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>19.95904350280762</v>
+        <v>19.95903968811035</v>
       </c>
       <c r="C163" t="n">
         <v>22.22999954223633</v>
@@ -4612,7 +4612,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>21.3866138458252</v>
+        <v>21.38661003112793</v>
       </c>
       <c r="C164" t="n">
         <v>23.81999969482422</v>
@@ -4639,7 +4639,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>18.34292602539062</v>
+        <v>18.34292793273926</v>
       </c>
       <c r="C165" t="n">
         <v>20.43000030517578</v>
@@ -4693,7 +4693,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>20.35153007507324</v>
+        <v>20.35152816772461</v>
       </c>
       <c r="C167" t="n">
         <v>22.6200008392334</v>
@@ -4720,7 +4720,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>20.28855323791504</v>
+        <v>20.28855514526367</v>
       </c>
       <c r="C168" t="n">
         <v>22.54999923706055</v>
@@ -4797,7 +4797,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>16.87072563171387</v>
+        <v>16.87072372436523</v>
       </c>
       <c r="C171" t="n">
         <v>18.70999908447266</v>
@@ -4822,7 +4822,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>8.906159400939941</v>
+        <v>8.906161308288574</v>
       </c>
       <c r="C172" t="n">
         <v>9.829999923706055</v>
@@ -4897,7 +4897,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>11.09872341156006</v>
+        <v>11.09872531890869</v>
       </c>
       <c r="C175" t="n">
         <v>12.25</v>
@@ -4922,7 +4922,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>10.42827320098877</v>
+        <v>10.42827033996582</v>
       </c>
       <c r="C176" t="n">
         <v>11.51000022888184</v>
@@ -4976,7 +4976,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>8.208527565002441</v>
+        <v>8.208526611328125</v>
       </c>
       <c r="C178" t="n">
         <v>9.060000419616699</v>
@@ -5003,7 +5003,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>7.610554218292236</v>
+        <v>7.610555171966553</v>
       </c>
       <c r="C179" t="n">
         <v>8.399999618530273</v>
@@ -5030,7 +5030,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>11.1077880859375</v>
+        <v>11.10778617858887</v>
       </c>
       <c r="C180" t="n">
         <v>12.26000022888184</v>
@@ -5057,7 +5057,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>12.43963050842285</v>
+        <v>12.4396333694458</v>
       </c>
       <c r="C181" t="n">
         <v>13.72999954223633</v>
@@ -5084,7 +5084,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>11.21650886535645</v>
+        <v>11.21650695800781</v>
       </c>
       <c r="C182" t="n">
         <v>12.38000011444092</v>
@@ -5111,7 +5111,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>13.68087577819824</v>
+        <v>13.68087863922119</v>
       </c>
       <c r="C183" t="n">
         <v>15.10000038146973</v>
@@ -5138,7 +5138,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>12.43057155609131</v>
+        <v>12.43057441711426</v>
       </c>
       <c r="C184" t="n">
         <v>13.72000026702881</v>
@@ -5165,7 +5165,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>13.54497623443604</v>
+        <v>13.54497337341309</v>
       </c>
       <c r="C185" t="n">
         <v>14.94999980926514</v>
@@ -5192,7 +5192,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>14.60501480102539</v>
+        <v>14.60501670837402</v>
       </c>
       <c r="C186" t="n">
         <v>16.1200008392334</v>
@@ -5246,7 +5246,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>12.51211357116699</v>
+        <v>12.51211166381836</v>
       </c>
       <c r="C188" t="n">
         <v>13.8100004196167</v>
@@ -5327,7 +5327,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>12.70238018035889</v>
+        <v>12.70237827301025</v>
       </c>
       <c r="C191" t="n">
         <v>14.02000045776367</v>
@@ -5354,7 +5354,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>10.79973793029785</v>
+        <v>10.79973888397217</v>
       </c>
       <c r="C192" t="n">
         <v>11.92000007629395</v>
@@ -5381,7 +5381,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>12.3291015625</v>
+        <v>12.32910251617432</v>
       </c>
       <c r="C193" t="n">
         <v>13.55000019073486</v>
@@ -5408,7 +5408,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>14.94050598144531</v>
+        <v>14.940505027771</v>
       </c>
       <c r="C194" t="n">
         <v>16.42000007629395</v>
@@ -5435,7 +5435,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>15.6047306060791</v>
+        <v>15.60472774505615</v>
       </c>
       <c r="C195" t="n">
         <v>17.14999961853027</v>
@@ -5462,7 +5462,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>17.8853816986084</v>
+        <v>17.88538360595703</v>
       </c>
       <c r="C196" t="n">
         <v>19.61000061035156</v>
@@ -5489,7 +5489,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>16.5355396270752</v>
+        <v>16.53553771972656</v>
       </c>
       <c r="C197" t="n">
         <v>18.1299991607666</v>
@@ -5516,7 +5516,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>18.24107551574707</v>
+        <v>18.24108123779297</v>
       </c>
       <c r="C198" t="n">
         <v>20</v>
@@ -5543,7 +5543,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>15.45919132232666</v>
+        <v>15.45919036865234</v>
       </c>
       <c r="C199" t="n">
         <v>16.90999984741211</v>
@@ -5570,7 +5570,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>17.01333808898926</v>
+        <v>17.01334190368652</v>
       </c>
       <c r="C200" t="n">
         <v>18.61000061035156</v>
@@ -5597,7 +5597,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>16.15399360656738</v>
+        <v>16.15398597717285</v>
       </c>
       <c r="C201" t="n">
         <v>17.67000007629395</v>
@@ -5624,7 +5624,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>14.8331413269043</v>
+        <v>14.83313941955566</v>
       </c>
       <c r="C202" t="n">
         <v>16.18000030517578</v>
@@ -5651,7 +5651,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>20.53537178039551</v>
+        <v>20.53536987304688</v>
       </c>
       <c r="C203" t="n">
         <v>22.39999961853027</v>
@@ -5680,7 +5680,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>20.59037971496582</v>
+        <v>20.59037399291992</v>
       </c>
       <c r="C204" t="n">
         <v>22.45999908447266</v>
@@ -5738,7 +5738,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>22.46080017089844</v>
+        <v>22.4607982635498</v>
       </c>
       <c r="C206" t="n">
         <v>24.44000053405762</v>
@@ -5767,7 +5767,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>20.10811424255371</v>
+        <v>20.10810852050781</v>
       </c>
       <c r="C207" t="n">
         <v>21.8799991607666</v>
@@ -5825,7 +5825,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>15.43633556365967</v>
+        <v>15.43633365631104</v>
       </c>
       <c r="C209" t="n">
         <v>16.75</v>
@@ -5912,7 +5912,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>18.56532859802246</v>
+        <v>18.56533241271973</v>
       </c>
       <c r="C212" t="n">
         <v>20.07999992370605</v>
@@ -6057,7 +6057,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>18.84747505187988</v>
+        <v>18.84747314453125</v>
       </c>
       <c r="C217" t="n">
         <v>20.28000068664551</v>
@@ -6086,7 +6086,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>18.13186264038086</v>
+        <v>18.13186073303223</v>
       </c>
       <c r="C218" t="n">
         <v>19.51000022888184</v>
@@ -6115,7 +6115,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>15.70622444152832</v>
+        <v>15.70622634887695</v>
       </c>
       <c r="C219" t="n">
         <v>16.89999961853027</v>
@@ -6260,7 +6260,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>19.48520278930664</v>
+        <v>19.48519897460938</v>
       </c>
       <c r="C224" t="n">
         <v>20.81999969482422</v>
@@ -6376,7 +6376,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>15.06354522705078</v>
+        <v>15.0635461807251</v>
       </c>
       <c r="C228" t="n">
         <v>16.02000045776367</v>
@@ -6405,7 +6405,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>13.79447555541992</v>
+        <v>13.79447460174561</v>
       </c>
       <c r="C229" t="n">
         <v>14.60000038146973</v>
@@ -6434,7 +6434,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>13.65275096893311</v>
+        <v>13.65275001525879</v>
       </c>
       <c r="C230" t="n">
         <v>14.44999980926514</v>
@@ -6492,7 +6492,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>14.4577751159668</v>
+        <v>14.45777416229248</v>
       </c>
       <c r="C232" t="n">
         <v>15.22000026702881</v>
@@ -6608,7 +6608,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>12.23139762878418</v>
+        <v>12.2313985824585</v>
       </c>
       <c r="C236" t="n">
         <v>12.57999992370605</v>
@@ -6666,7 +6666,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>12.95583724975586</v>
+        <v>12.95583629608154</v>
       </c>
       <c r="C238" t="n">
         <v>13.25</v>
@@ -6695,7 +6695,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>14.27586555480957</v>
+        <v>14.27586460113525</v>
       </c>
       <c r="C239" t="n">
         <v>14.60000038146973</v>
@@ -6724,7 +6724,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>15.01899147033691</v>
+        <v>15.01899242401123</v>
       </c>
       <c r="C240" t="n">
         <v>15.35999965667725</v>
@@ -6753,7 +6753,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>15.3536434173584</v>
+        <v>15.35364437103271</v>
       </c>
       <c r="C241" t="n">
         <v>15.63000011444092</v>
@@ -6898,7 +6898,7 @@
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>19.70180511474609</v>
+        <v>19.70180320739746</v>
       </c>
       <c r="C246" t="n">
         <v>19.95999908447266</v>
